--- a/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-picarro.xlsx
+++ b/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-picarro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-29-cattle-slurry-retrail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F3315A-B05D-45AE-A9EC-E5CB20458D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6E7EE3-C9D5-455F-AED1-C279FBB9B92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}</author>
+    <author>tc={CC3580E3-8AE8-48FD-A9E3-572FDF71E9E0}</author>
+    <author>tc={EC29F398-FAA7-4689-B818-938037A418D3}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0" shapeId="0" xr:uid="{7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}">
@@ -49,12 +51,28 @@
     Standard liters per minute</t>
       </text>
     </comment>
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{CC3580E3-8AE8-48FD-A9E3-572FDF71E9E0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Real time</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="2" shapeId="0" xr:uid="{EC29F398-FAA7-4689-B818-938037A418D3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Realtime, at valve 5</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
   <si>
     <t>Valve code</t>
   </si>
@@ -123,6 +141,15 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10:10:00</t>
+  </si>
+  <si>
+    <t>starttime</t>
+  </si>
+  <si>
+    <t>endtime</t>
   </si>
 </sst>
 </file>
@@ -132,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +172,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -179,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -189,6 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,12 +512,18 @@
   <threadedComment ref="F1" dT="2026-03-12T10:45:59.68" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}">
     <text>Standard liters per minute</text>
   </threadedComment>
+  <threadedComment ref="M2" dT="2026-05-06T08:10:36.00" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{CC3580E3-8AE8-48FD-A9E3-572FDF71E9E0}">
+    <text>Real time</text>
+  </threadedComment>
+  <threadedComment ref="P2" dT="2026-05-06T08:12:33.27" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{EC29F398-FAA7-4689-B818-938037A418D3}">
+    <text>Realtime, at valve 5</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -495,11 +535,12 @@
     <col min="8" max="9" width="21" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,11 +580,17 @@
       <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -569,14 +616,34 @@
         <f>F2+G2</f>
         <v>1.1910000000000001</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I2" s="1">
+        <v>0.222</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="K2" s="9">
+        <f>I2+J2</f>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L2" s="1">
+        <f>(H2+K2)/2</f>
+        <v>1.1825000000000001</v>
+      </c>
+      <c r="M2" s="3">
+        <v>46141</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="3">
+        <v>46147.59652777778</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.59652777777777777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -602,12 +669,22 @@
         <f t="shared" ref="H3:H25" si="0">F3+G3</f>
         <v>1.1930000000000001</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I3" s="1">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K25" si="1">I3+J3</f>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L25" si="2">(H3+K3)/2</f>
+        <v>1.1844999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -633,12 +710,22 @@
         <f t="shared" si="0"/>
         <v>1.1910000000000001</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I4" s="1">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="1"/>
+        <v>1.177</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1840000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -664,12 +751,22 @@
         <f t="shared" si="0"/>
         <v>1.9279999999999999</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I5" s="1">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.5514999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -695,12 +792,22 @@
         <f t="shared" si="0"/>
         <v>1.93</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I6" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="2"/>
+        <v>1.5505</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -726,12 +833,22 @@
         <f t="shared" si="0"/>
         <v>1.198</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I7" s="4">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2150000000000001</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="2"/>
+        <v>1.2065000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -754,12 +871,22 @@
         <f t="shared" si="0"/>
         <v>1.1910000000000001</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I8" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="K8" s="9">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1830000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -782,12 +909,22 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I9" s="1">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="1"/>
+        <v>1.177</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1844999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -810,12 +947,22 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I10" s="1">
+        <v>0.215</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="K10" s="9">
+        <f t="shared" si="1"/>
+        <v>1.177</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1844999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -838,12 +985,22 @@
         <f t="shared" si="0"/>
         <v>1.1930000000000001</v>
       </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I11" s="1">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1844999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -866,12 +1023,22 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I12" s="1">
+        <v>0.216</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="1"/>
+        <v>1.177</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1844999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -897,12 +1064,22 @@
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I13" s="5">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1830000000000001</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>1.1915</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -928,12 +1105,22 @@
         <f t="shared" si="0"/>
         <v>1.194</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I14" s="1">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1839999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -959,12 +1146,22 @@
         <f t="shared" si="0"/>
         <v>1.1930000000000001</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I15" s="1">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1835</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -990,10 +1187,20 @@
         <f t="shared" si="0"/>
         <v>1.19</v>
       </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="I16" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1709999999999998</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1804999999999999</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -1021,10 +1228,20 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="I17" s="1">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1835</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -1052,10 +1269,20 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="I18" s="1">
+        <v>0.214</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1835</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -1083,10 +1310,20 @@
         <f t="shared" si="0"/>
         <v>1.198</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="I19" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1819999999999999</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>1.19</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -1114,10 +1351,20 @@
         <f t="shared" si="0"/>
         <v>1.1910000000000001</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="I20" s="1">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1825000000000001</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -1145,10 +1392,20 @@
         <f t="shared" si="0"/>
         <v>1.194</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="I21" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1839999999999999</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -1176,10 +1433,20 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="I22" s="1">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1839999999999999</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -1207,10 +1474,20 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="I23" s="1">
+        <v>0.215</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="1"/>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1839999999999999</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -1238,10 +1515,20 @@
         <f t="shared" si="0"/>
         <v>1.1919999999999999</v>
       </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="I24" s="1">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1835</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -1269,10 +1556,20 @@
         <f t="shared" si="0"/>
         <v>1.1970000000000001</v>
       </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="I25" s="5">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>1.1920000000000002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
